--- a/Datos/Tabla1.xlsx
+++ b/Datos/Tabla1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Laboratorio de Ambientes Inteligentes\Proyecto Inundaciones\Proyecto_Recomendaciones_Inundaciones\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{04477BA5-040B-4A4A-AD59-1C6FF7D2494A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFB9DFC6-A6C1-4598-B9F4-374E1A2D3678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{D3AFEBD6-96F4-4E36-97A2-D1F1D80A7D7C}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="99">
   <si>
     <t>Municipio</t>
   </si>
@@ -68,15 +68,9 @@
     <t>ICI_Comp</t>
   </si>
   <si>
-    <t>C</t>
-  </si>
-  <si>
     <t>Calakmul</t>
   </si>
   <si>
-    <t>II</t>
-  </si>
-  <si>
     <t>Candelaria</t>
   </si>
   <si>
@@ -86,9 +80,6 @@
     <t>Hecelchakán</t>
   </si>
   <si>
-    <t>I</t>
-  </si>
-  <si>
     <t>Champotón</t>
   </si>
   <si>
@@ -98,18 +89,12 @@
     <t>Tenabo</t>
   </si>
   <si>
-    <t>III</t>
-  </si>
-  <si>
     <t>Seybaplaya</t>
   </si>
   <si>
     <t>Escárcega</t>
   </si>
   <si>
-    <t>IV</t>
-  </si>
-  <si>
     <t>Palizada</t>
   </si>
   <si>
@@ -117,6 +102,240 @@
   </si>
   <si>
     <t>Carmen</t>
+  </si>
+  <si>
+    <t>0.5975410164506229</t>
+  </si>
+  <si>
+    <t>0.36589065209796373</t>
+  </si>
+  <si>
+    <t>0.46738336446395223</t>
+  </si>
+  <si>
+    <t>0.28364520329827253</t>
+  </si>
+  <si>
+    <t>0.46535845561308986</t>
+  </si>
+  <si>
+    <t>0.4589544114074731</t>
+  </si>
+  <si>
+    <t>0.3434159530357355</t>
+  </si>
+  <si>
+    <t>0.3940853098403368</t>
+  </si>
+  <si>
+    <t>0.18873855361191405</t>
+  </si>
+  <si>
+    <t>0.23075973197388508</t>
+  </si>
+  <si>
+    <t>0.10479821543884449</t>
+  </si>
+  <si>
+    <t>0.7587383084481308</t>
+  </si>
+  <si>
+    <t>0.7540990388433584</t>
+  </si>
+  <si>
+    <t>0.4652088422307521</t>
+  </si>
+  <si>
+    <t>0.6090998458001601</t>
+  </si>
+  <si>
+    <t>0.38700824761469954</t>
+  </si>
+  <si>
+    <t>0.39031063543236844</t>
+  </si>
+  <si>
+    <t>0.6454923721518147</t>
+  </si>
+  <si>
+    <t>0.6108030880295756</t>
+  </si>
+  <si>
+    <t>0.7343760245649223</t>
+  </si>
+  <si>
+    <t>0.019120474386474625</t>
+  </si>
+  <si>
+    <t>0.16307744317283104</t>
+  </si>
+  <si>
+    <t>0.5506811527669552</t>
+  </si>
+  <si>
+    <t>0.4589432328446952</t>
+  </si>
+  <si>
+    <t>0.44085748062138636</t>
+  </si>
+  <si>
+    <t>0.43159846512049066</t>
+  </si>
+  <si>
+    <t>0.47342134570685906</t>
+  </si>
+  <si>
+    <t>0.38258256461129075</t>
+  </si>
+  <si>
+    <t>0.39678845158778037</t>
+  </si>
+  <si>
+    <t>0.3669895918290161</t>
+  </si>
+  <si>
+    <t>0.39279201011345233</t>
+  </si>
+  <si>
+    <t>0.6666666666666666</t>
+  </si>
+  <si>
+    <t>0.5603450357777953</t>
+  </si>
+  <si>
+    <t>0.7159659306312525</t>
+  </si>
+  <si>
+    <t>0.6661575350124028</t>
+  </si>
+  <si>
+    <t>0.5324076073085952</t>
+  </si>
+  <si>
+    <t>0.5444458735114439</t>
+  </si>
+  <si>
+    <t>0.49468436977110625</t>
+  </si>
+  <si>
+    <t>0.5139428394005123</t>
+  </si>
+  <si>
+    <t>0.5682258759696054</t>
+  </si>
+  <si>
+    <t>0.4063089471640359</t>
+  </si>
+  <si>
+    <t>0.4260431502073576</t>
+  </si>
+  <si>
+    <t>0.4328359579936761</t>
+  </si>
+  <si>
+    <t>0.25316855017207973</t>
+  </si>
+  <si>
+    <t>0.2897000466657409</t>
+  </si>
+  <si>
+    <t>0.2507053535477647</t>
+  </si>
+  <si>
+    <t>0.15449799794630362</t>
+  </si>
+  <si>
+    <t>0.5522856000412675</t>
+  </si>
+  <si>
+    <t>0.31578987749715265</t>
+  </si>
+  <si>
+    <t>0.26827167759956067</t>
+  </si>
+  <si>
+    <t>0.2759895056942995</t>
+  </si>
+  <si>
+    <t>0.31062206395790115</t>
+  </si>
+  <si>
+    <t>0.38465785034221756</t>
+  </si>
+  <si>
+    <t>0.6654667217547218</t>
+  </si>
+  <si>
+    <t>0.2908562043840893</t>
+  </si>
+  <si>
+    <t>0.33471739881643103</t>
+  </si>
+  <si>
+    <t>0.5310349115183228</t>
+  </si>
+  <si>
+    <t>0.2595482353110793</t>
+  </si>
+  <si>
+    <t>0.3065859911278983</t>
+  </si>
+  <si>
+    <t>0.2667503180369583</t>
+  </si>
+  <si>
+    <t>0.26639921166146974</t>
+  </si>
+  <si>
+    <t>0.2395187101370097</t>
+  </si>
+  <si>
+    <t>0.2779903544371479</t>
+  </si>
+  <si>
+    <t>0.5607607955340346</t>
+  </si>
+  <si>
+    <t>0.3063215803068533</t>
+  </si>
+  <si>
+    <t>0.12997886945904635</t>
+  </si>
+  <si>
+    <t>0.49624664745223396</t>
+  </si>
+  <si>
+    <t>0.25512679442942193</t>
+  </si>
+  <si>
+    <t>0.23054199453710095</t>
+  </si>
+  <si>
+    <t>0.5669475957274223</t>
+  </si>
+  <si>
+    <t>0.2912700977670555</t>
+  </si>
+  <si>
+    <t>0.2673354446305152</t>
+  </si>
+  <si>
+    <t>0.25775410791565456</t>
+  </si>
+  <si>
+    <t>0.2550259597854911</t>
+  </si>
+  <si>
+    <t>0.33132410238968274</t>
+  </si>
+  <si>
+    <t>0.6131137586443781</t>
+  </si>
+  <si>
+    <t>0.2985888923454713</t>
+  </si>
+  <si>
+    <t>0.2323481341377387</t>
   </si>
 </sst>
 </file>
@@ -176,54 +395,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="11">
     <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -253,6 +432,25 @@
     <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -267,22 +465,21 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4BA8149E-779E-475F-A60C-3438B14A5984}" name="Tabla1" displayName="Tabla1" ref="A1:J13" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1">
-  <autoFilter ref="A1:J13" xr:uid="{4BA8149E-779E-475F-A60C-3438B14A5984}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4BA8149E-779E-475F-A60C-3438B14A5984}" name="Tabla1" displayName="Tabla1" ref="A1:I13" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
+  <autoFilter ref="A1:I13" xr:uid="{4BA8149E-779E-475F-A60C-3438B14A5984}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I13">
     <sortCondition ref="A1:A13"/>
   </sortState>
-  <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{39D106A7-194E-46E5-8605-4ED96635F332}" name="Municipio" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{57551B40-141C-46B9-9D9D-2F7A24A200C8}" name="IVS" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{C30EEC64-C227-45FB-9F98-F4F5CEF104BE}" name="DIM_SS" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{4D6F3DDB-69ED-4AF8-B4A4-84641CFB14CD}" name="DIM_EF" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{79C057E6-C218-44B0-8D73-3A00881DA5A8}" name="DIM_CA" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{B87DB94D-CC00-4E94-90A2-7CB24B0D6A62}" name="DIM_GV" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{5BB92E3D-5CDD-4C9B-A074-933413109150}" name="ICI_Gen" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{40327DFA-6B4E-4081-BBD4-4385F5123D7D}" name="ICI_Rsg" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{789913F7-CC80-4792-905A-7F9DA0C3FD7D}" name="ICI_Comp" dataDxfId="3"/>
-    <tableColumn id="10" xr3:uid="{65B6816C-0422-41CF-8732-C2A19A9DFF69}" name="C" dataDxfId="2"/>
+  <tableColumns count="9">
+    <tableColumn id="1" xr3:uid="{39D106A7-194E-46E5-8605-4ED96635F332}" name="Municipio" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{57551B40-141C-46B9-9D9D-2F7A24A200C8}" name="IVS" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{C30EEC64-C227-45FB-9F98-F4F5CEF104BE}" name="DIM_SS" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{4D6F3DDB-69ED-4AF8-B4A4-84641CFB14CD}" name="DIM_EF" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{79C057E6-C218-44B0-8D73-3A00881DA5A8}" name="DIM_CA" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{B87DB94D-CC00-4E94-90A2-7CB24B0D6A62}" name="DIM_GV" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{5BB92E3D-5CDD-4C9B-A074-933413109150}" name="ICI_Gen" dataDxfId="2"/>
+    <tableColumn id="8" xr3:uid="{40327DFA-6B4E-4081-BBD4-4385F5123D7D}" name="ICI_Rsg" dataDxfId="1"/>
+    <tableColumn id="9" xr3:uid="{789913F7-CC80-4792-905A-7F9DA0C3FD7D}" name="ICI_Comp" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -585,13 +782,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28EBBEA0-3CDE-4526-9D14-D2CFDC34215C}">
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="11.08984375" customWidth="1"/>
+    <col min="9" max="9" width="15.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -619,396 +817,357 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
+      <c r="B2">
+        <v>0.6754</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E2">
+        <v>0.81356359295608605</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2">
+        <v>0.46145838338614498</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3">
+        <v>0.46239999999999998</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4">
+        <v>0.29349999999999998</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="2">
-        <v>0.67500000000000004</v>
-      </c>
-      <c r="C2" s="2">
-        <v>0.71599999999999997</v>
-      </c>
-      <c r="D2" s="2">
-        <v>0.55100000000000005</v>
-      </c>
-      <c r="E2" s="2">
-        <v>0.61</v>
-      </c>
-      <c r="F2" s="2">
-        <v>0.52400000000000002</v>
-      </c>
-      <c r="G2" s="2">
-        <v>0.82399999999999995</v>
-      </c>
-      <c r="H2" s="2">
-        <v>0.86599999999999999</v>
-      </c>
-      <c r="I2" s="2">
-        <v>0.84499999999999997</v>
-      </c>
-      <c r="J2" s="3" t="s">
+      <c r="B5">
+        <v>0.55720000000000003</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5">
+        <v>0.37798505457951698</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="H5">
+        <v>0.58160959141357704</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6">
+        <v>0.28870000000000001</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7">
+        <v>0.46529999999999999</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8">
+        <v>0.4511</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9">
+        <v>0.47760000000000002</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F9">
+        <v>0.43890899254683102</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="H9">
+        <v>0.19942985561308099</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" s="2">
-        <v>0.46200000000000002</v>
-      </c>
-      <c r="C3" s="2">
-        <v>0.51400000000000001</v>
-      </c>
-      <c r="D3" s="2">
-        <v>0.47299999999999998</v>
-      </c>
-      <c r="E3" s="2">
-        <v>0.503</v>
-      </c>
-      <c r="F3" s="2">
-        <v>0.35299999999999998</v>
-      </c>
-      <c r="G3" s="2">
-        <v>0.224</v>
-      </c>
-      <c r="H3" s="2">
-        <v>0.31</v>
-      </c>
-      <c r="I3" s="2">
-        <v>0.26700000000000002</v>
-      </c>
-      <c r="J3" s="3" t="s">
+      <c r="B10">
+        <v>0.55649999999999999</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11">
+        <v>0.44940000000000002</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12">
+        <v>0.4511</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" s="2">
-        <v>0.29299999999999998</v>
-      </c>
-      <c r="C4" s="2">
-        <v>0.253</v>
-      </c>
-      <c r="D4" s="2">
-        <v>0.66700000000000004</v>
-      </c>
-      <c r="E4" s="2">
-        <v>0.312</v>
-      </c>
-      <c r="F4" s="2">
-        <v>0.38900000000000001</v>
-      </c>
-      <c r="G4" s="2">
-        <v>0.16300000000000001</v>
-      </c>
-      <c r="H4" s="2">
-        <v>0.41799999999999998</v>
-      </c>
-      <c r="I4" s="2">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="2">
-        <v>0.55700000000000005</v>
-      </c>
-      <c r="C5" s="2">
-        <v>0.66600000000000004</v>
-      </c>
-      <c r="D5" s="2">
-        <v>0.378</v>
-      </c>
-      <c r="E5" s="2">
-        <v>0.59199999999999997</v>
-      </c>
-      <c r="F5" s="2">
-        <v>0.55100000000000005</v>
-      </c>
-      <c r="G5" s="2">
-        <v>0.79</v>
-      </c>
-      <c r="H5" s="2">
-        <v>0.65700000000000003</v>
-      </c>
-      <c r="I5" s="2">
-        <v>0.72399999999999998</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="2">
-        <v>0.28899999999999998</v>
-      </c>
-      <c r="C6" s="2">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="D6" s="2">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="E6" s="2">
-        <v>0.29799999999999999</v>
-      </c>
-      <c r="F6" s="2">
-        <v>0.307</v>
-      </c>
-      <c r="G6" s="2">
-        <v>0.35799999999999998</v>
-      </c>
-      <c r="H6" s="2">
-        <v>0.55100000000000005</v>
-      </c>
-      <c r="I6" s="2">
-        <v>0.45400000000000001</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A7" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="2">
-        <v>0.46500000000000002</v>
-      </c>
-      <c r="C7" s="2">
-        <v>0.495</v>
-      </c>
-      <c r="D7" s="2">
-        <v>0.432</v>
-      </c>
-      <c r="E7" s="2">
-        <v>0.498</v>
-      </c>
-      <c r="F7" s="2">
-        <v>0.435</v>
-      </c>
-      <c r="G7" s="2">
-        <v>0.18099999999999999</v>
-      </c>
-      <c r="H7" s="2">
-        <v>0.36199999999999999</v>
-      </c>
-      <c r="I7" s="2">
-        <v>0.27100000000000002</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="2">
-        <v>0.45100000000000001</v>
-      </c>
-      <c r="C8" s="2">
-        <v>0.40600000000000003</v>
-      </c>
-      <c r="D8" s="2">
-        <v>0.39700000000000002</v>
-      </c>
-      <c r="E8" s="2">
-        <v>0.52100000000000002</v>
-      </c>
-      <c r="F8" s="2">
-        <v>0.48</v>
-      </c>
-      <c r="G8" s="2">
-        <v>0.373</v>
-      </c>
-      <c r="H8" s="2">
-        <v>0.36299999999999999</v>
-      </c>
-      <c r="I8" s="2">
-        <v>0.36799999999999999</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="2">
-        <v>0.47799999999999998</v>
-      </c>
-      <c r="C9" s="2">
-        <v>0.54400000000000004</v>
-      </c>
-      <c r="D9" s="2">
-        <v>0.441</v>
-      </c>
-      <c r="E9" s="2">
-        <v>0.55100000000000005</v>
-      </c>
-      <c r="F9" s="2">
-        <v>0.376</v>
-      </c>
-      <c r="G9" s="2">
-        <v>0.32100000000000001</v>
-      </c>
-      <c r="H9" s="2">
-        <v>0.20100000000000001</v>
-      </c>
-      <c r="I9" s="2">
-        <v>0.26100000000000001</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="2">
-        <v>0.55600000000000005</v>
-      </c>
-      <c r="C10" s="2">
-        <v>0.53200000000000003</v>
-      </c>
-      <c r="D10" s="2">
-        <v>0.45900000000000002</v>
-      </c>
-      <c r="E10" s="2">
-        <v>0.623</v>
-      </c>
-      <c r="F10" s="2">
-        <v>0.61</v>
-      </c>
-      <c r="G10" s="2">
-        <v>0.47099999999999997</v>
-      </c>
-      <c r="H10" s="2">
-        <v>0.376</v>
-      </c>
-      <c r="I10" s="2">
-        <v>0.42399999999999999</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A11" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" s="2">
-        <v>0.44900000000000001</v>
-      </c>
-      <c r="C11" s="2">
-        <v>0.433</v>
-      </c>
-      <c r="D11" s="2">
-        <v>0.39300000000000002</v>
-      </c>
-      <c r="E11" s="2">
-        <v>0.48899999999999999</v>
-      </c>
-      <c r="F11" s="2">
-        <v>0.48099999999999998</v>
-      </c>
-      <c r="G11" s="2">
-        <v>0.61499999999999999</v>
-      </c>
-      <c r="H11" s="2">
-        <v>0.65</v>
-      </c>
-      <c r="I11" s="2">
-        <v>0.63300000000000001</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A12" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" s="2">
-        <v>0.45100000000000001</v>
-      </c>
-      <c r="C12" s="2">
-        <v>0.42599999999999999</v>
-      </c>
-      <c r="D12" s="2">
-        <v>0.36699999999999999</v>
-      </c>
-      <c r="E12" s="2">
-        <v>0.54200000000000004</v>
-      </c>
-      <c r="F12" s="2">
-        <v>0.46899999999999997</v>
-      </c>
-      <c r="G12" s="2">
-        <v>0.14399999999999999</v>
-      </c>
-      <c r="H12" s="2">
-        <v>0.27100000000000002</v>
-      </c>
-      <c r="I12" s="2">
-        <v>0.20799999999999999</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A13" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" s="2">
-        <v>0.45600000000000002</v>
-      </c>
-      <c r="C13" s="2">
-        <v>0.56799999999999995</v>
-      </c>
-      <c r="D13" s="2">
-        <v>0.38300000000000001</v>
-      </c>
-      <c r="E13" s="2">
-        <v>0.56100000000000005</v>
-      </c>
-      <c r="F13" s="2">
-        <v>0.312</v>
-      </c>
-      <c r="G13" s="2">
-        <v>0.59599999999999997</v>
-      </c>
-      <c r="H13" s="2">
-        <v>0.112</v>
-      </c>
-      <c r="I13" s="2">
-        <v>0.35399999999999998</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B16" s="4"/>
+      <c r="B13">
+        <v>0.45550000000000002</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B16" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Datos/Tabla1.xlsx
+++ b/Datos/Tabla1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Laboratorio de Ambientes Inteligentes\Proyecto Inundaciones\Proyecto_Recomendaciones_Inundaciones\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFB9DFC6-A6C1-4598-B9F4-374E1A2D3678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CA38F24-1C96-4C29-9298-1BB6F96C2632}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{D3AFEBD6-96F4-4E36-97A2-D1F1D80A7D7C}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="104">
   <si>
     <t>Municipio</t>
   </si>
@@ -336,6 +336,21 @@
   </si>
   <si>
     <t>0.2323481341377387</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>II</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>III</t>
+  </si>
+  <si>
+    <t>IV</t>
   </si>
 </sst>
 </file>
@@ -401,7 +416,10 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="11">
+  <dxfs count="12">
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -465,21 +483,22 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4BA8149E-779E-475F-A60C-3438B14A5984}" name="Tabla1" displayName="Tabla1" ref="A1:I13" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
-  <autoFilter ref="A1:I13" xr:uid="{4BA8149E-779E-475F-A60C-3438B14A5984}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4BA8149E-779E-475F-A60C-3438B14A5984}" name="Tabla1" displayName="Tabla1" ref="A1:J13" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
+  <autoFilter ref="A1:J13" xr:uid="{4BA8149E-779E-475F-A60C-3438B14A5984}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I13">
     <sortCondition ref="A1:A13"/>
   </sortState>
-  <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{39D106A7-194E-46E5-8605-4ED96635F332}" name="Municipio" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{57551B40-141C-46B9-9D9D-2F7A24A200C8}" name="IVS" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{C30EEC64-C227-45FB-9F98-F4F5CEF104BE}" name="DIM_SS" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{4D6F3DDB-69ED-4AF8-B4A4-84641CFB14CD}" name="DIM_EF" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{79C057E6-C218-44B0-8D73-3A00881DA5A8}" name="DIM_CA" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{B87DB94D-CC00-4E94-90A2-7CB24B0D6A62}" name="DIM_GV" dataDxfId="3"/>
-    <tableColumn id="7" xr3:uid="{5BB92E3D-5CDD-4C9B-A074-933413109150}" name="ICI_Gen" dataDxfId="2"/>
-    <tableColumn id="8" xr3:uid="{40327DFA-6B4E-4081-BBD4-4385F5123D7D}" name="ICI_Rsg" dataDxfId="1"/>
-    <tableColumn id="9" xr3:uid="{789913F7-CC80-4792-905A-7F9DA0C3FD7D}" name="ICI_Comp" dataDxfId="0"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{39D106A7-194E-46E5-8605-4ED96635F332}" name="Municipio" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{57551B40-141C-46B9-9D9D-2F7A24A200C8}" name="IVS" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{C30EEC64-C227-45FB-9F98-F4F5CEF104BE}" name="DIM_SS" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{4D6F3DDB-69ED-4AF8-B4A4-84641CFB14CD}" name="DIM_EF" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{79C057E6-C218-44B0-8D73-3A00881DA5A8}" name="DIM_CA" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{B87DB94D-CC00-4E94-90A2-7CB24B0D6A62}" name="DIM_GV" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{5BB92E3D-5CDD-4C9B-A074-933413109150}" name="ICI_Gen" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{40327DFA-6B4E-4081-BBD4-4385F5123D7D}" name="ICI_Rsg" dataDxfId="2"/>
+    <tableColumn id="9" xr3:uid="{789913F7-CC80-4792-905A-7F9DA0C3FD7D}" name="ICI_Comp" dataDxfId="1"/>
+    <tableColumn id="10" xr3:uid="{7DD18844-935A-49AE-B047-6FD9BEDE0E9C}" name="C" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -782,14 +801,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28EBBEA0-3CDE-4526-9D14-D2CFDC34215C}">
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="11.08984375" customWidth="1"/>
     <col min="9" max="9" width="15.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -817,8 +836,11 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J1" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
@@ -846,8 +868,11 @@
       <c r="I2" s="4" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J2" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>14</v>
       </c>
@@ -875,8 +900,11 @@
       <c r="I3" s="4" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J3" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>19</v>
       </c>
@@ -904,8 +932,11 @@
       <c r="I4" s="4" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J4" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -933,8 +964,11 @@
       <c r="I5" s="4" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J5" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>20</v>
       </c>
@@ -962,8 +996,11 @@
       <c r="I6" s="4" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J6" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
@@ -991,8 +1028,11 @@
       <c r="I7" s="4" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J7" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>17</v>
       </c>
@@ -1020,8 +1060,11 @@
       <c r="I8" s="4" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+      <c r="J8" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>12</v>
       </c>
@@ -1049,8 +1092,11 @@
       <c r="I9" s="4" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J9" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>11</v>
       </c>
@@ -1078,8 +1124,11 @@
       <c r="I10" s="4" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J10" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>18</v>
       </c>
@@ -1107,8 +1156,11 @@
       <c r="I11" s="4" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J11" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>16</v>
       </c>
@@ -1136,8 +1188,11 @@
       <c r="I12" s="4" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J12" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>15</v>
       </c>
@@ -1165,8 +1220,11 @@
       <c r="I13" s="4" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J13" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B16" s="3"/>
     </row>
   </sheetData>
